--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/3_fold/107.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/3_fold/107.xlsx
@@ -426,13 +426,13 @@
         <v>-17.64874053666097</v>
       </c>
       <c r="E2">
-        <v>-7.394415958086306</v>
+        <v>-11.79558097597903</v>
       </c>
       <c r="F2">
-        <v>-4.822809590727784</v>
+        <v>-6.060128932048231</v>
       </c>
       <c r="G2">
-        <v>-10.04871190093268</v>
+        <v>-12.72493374106073</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>-16.84237751342026</v>
       </c>
       <c r="E3">
-        <v>-7.241448634581209</v>
+        <v>-13.9249102106517</v>
       </c>
       <c r="F3">
-        <v>-4.894730427465636</v>
+        <v>-5.471570759722765</v>
       </c>
       <c r="G3">
-        <v>-11.35996270976383</v>
+        <v>-12.75516564292536</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>-16.03182364999949</v>
       </c>
       <c r="E4">
-        <v>-8.565995582506735</v>
+        <v>-15.4136324552513</v>
       </c>
       <c r="F4">
-        <v>-5.034702315536963</v>
+        <v>-5.655734377658515</v>
       </c>
       <c r="G4">
-        <v>-9.874918191757562</v>
+        <v>-12.67006475929285</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>-15.33962934736053</v>
       </c>
       <c r="E5">
-        <v>-8.73378007296493</v>
+        <v>-15.61859571731247</v>
       </c>
       <c r="F5">
-        <v>-4.951880830983142</v>
+        <v>-5.354725729134601</v>
       </c>
       <c r="G5">
-        <v>-11.20737966585882</v>
+        <v>-13.44534817695262</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>-14.76194213154177</v>
       </c>
       <c r="E6">
-        <v>-9.392813423775204</v>
+        <v>-14.66796033972628</v>
       </c>
       <c r="F6">
-        <v>-4.761216892117472</v>
+        <v>-5.310986939161994</v>
       </c>
       <c r="G6">
-        <v>-10.6803871636444</v>
+        <v>-14.53720747762349</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>-14.31127894100589</v>
       </c>
       <c r="E7">
-        <v>-10.23616472364568</v>
+        <v>-16.95738018751812</v>
       </c>
       <c r="F7">
-        <v>-4.691582926721514</v>
+        <v>-5.393731613978916</v>
       </c>
       <c r="G7">
-        <v>-11.77595593059203</v>
+        <v>-12.66579084500165</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>-13.96661013069775</v>
       </c>
       <c r="E8">
-        <v>-10.84534863257952</v>
+        <v>-17.69457499970078</v>
       </c>
       <c r="F8">
-        <v>-4.652862108941977</v>
+        <v>-5.290451816409449</v>
       </c>
       <c r="G8">
-        <v>-11.29367234588547</v>
+        <v>-13.58346910266932</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>-13.70874391408784</v>
       </c>
       <c r="E9">
-        <v>-11.98844868396571</v>
+        <v>-18.30438836652169</v>
       </c>
       <c r="F9">
-        <v>-4.739024421124419</v>
+        <v>-5.359666891590772</v>
       </c>
       <c r="G9">
-        <v>-11.76690489908766</v>
+        <v>-14.58475022211297</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>-13.49064344563582</v>
       </c>
       <c r="E10">
-        <v>-13.90314636457083</v>
+        <v>-18.89955664840178</v>
       </c>
       <c r="F10">
-        <v>-4.423103597700726</v>
+        <v>-4.752120085339187</v>
       </c>
       <c r="G10">
-        <v>-10.25317450398361</v>
+        <v>-14.6410774991909</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>-13.26892329095371</v>
       </c>
       <c r="E11">
-        <v>-14.24333438897505</v>
+        <v>-20.45804456356356</v>
       </c>
       <c r="F11">
-        <v>-4.166842559817554</v>
+        <v>-4.879216444317992</v>
       </c>
       <c r="G11">
-        <v>-11.09544018953945</v>
+        <v>-13.4317749402416</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>-12.99169908146373</v>
       </c>
       <c r="E12">
-        <v>-14.44066264385928</v>
+        <v>-20.38211111140295</v>
       </c>
       <c r="F12">
-        <v>-4.378391620443082</v>
+        <v>-5.048182820289184</v>
       </c>
       <c r="G12">
-        <v>-11.28121807356673</v>
+        <v>-13.22640855825846</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>-12.59520206115536</v>
       </c>
       <c r="E13">
-        <v>-15.90002226299315</v>
+        <v>-20.39098239198397</v>
       </c>
       <c r="F13">
-        <v>-4.141468423640383</v>
+        <v>-4.471164321116567</v>
       </c>
       <c r="G13">
-        <v>-10.2782022282605</v>
+        <v>-13.78009895497433</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>-12.03350828310668</v>
       </c>
       <c r="E14">
-        <v>-16.01365978974163</v>
+        <v>-22.48505292803292</v>
       </c>
       <c r="F14">
-        <v>-4.396920979653724</v>
+        <v>-4.924732152327721</v>
       </c>
       <c r="G14">
-        <v>-10.34372454557375</v>
+        <v>-11.72026924407595</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>-11.2657642765072</v>
       </c>
       <c r="E15">
-        <v>-17.03866176748179</v>
+        <v>-21.65089895887203</v>
       </c>
       <c r="F15">
-        <v>-4.259155985775561</v>
+        <v>-4.774021154443799</v>
       </c>
       <c r="G15">
-        <v>-9.739361283561024</v>
+        <v>-12.00446964698576</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>-10.27134111825255</v>
       </c>
       <c r="E16">
-        <v>-17.78235041139146</v>
+        <v>-21.70381417765165</v>
       </c>
       <c r="F16">
-        <v>-4.199439978675044</v>
+        <v>-4.151627897087927</v>
       </c>
       <c r="G16">
-        <v>-8.199828496523891</v>
+        <v>-11.8291464657715</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>-9.072653812275085</v>
       </c>
       <c r="E17">
-        <v>-18.38401252499855</v>
+        <v>-23.2364263923336</v>
       </c>
       <c r="F17">
-        <v>-4.151183667578646</v>
+        <v>-4.220061413399981</v>
       </c>
       <c r="G17">
-        <v>-7.821625153026472</v>
+        <v>-10.84135250885484</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>-7.716575860398443</v>
       </c>
       <c r="E18">
-        <v>-19.62384530966259</v>
+        <v>-24.53795510687814</v>
       </c>
       <c r="F18">
-        <v>-3.739873861309164</v>
+        <v>-4.474717365337856</v>
       </c>
       <c r="G18">
-        <v>-6.817195704774976</v>
+        <v>-10.00698578495571</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>-6.280023763678179</v>
       </c>
       <c r="E19">
-        <v>-20.17243370789979</v>
+        <v>-24.08407521403736</v>
       </c>
       <c r="F19">
-        <v>-3.559894394402005</v>
+        <v>-4.03992674331311</v>
       </c>
       <c r="G19">
-        <v>-6.903322857524655</v>
+        <v>-9.50122381128463</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>-4.860040728359196</v>
       </c>
       <c r="E20">
-        <v>-22.25713935970088</v>
+        <v>-25.30895044905406</v>
       </c>
       <c r="F20">
-        <v>-3.297118782235673</v>
+        <v>-4.259372161633019</v>
       </c>
       <c r="G20">
-        <v>-5.665993220039892</v>
+        <v>-9.194591151800715</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>-3.548408784555161</v>
       </c>
       <c r="E21">
-        <v>-22.21581250590688</v>
+        <v>-26.46518307506249</v>
       </c>
       <c r="F21">
-        <v>-3.290619253158709</v>
+        <v>-3.279322678863879</v>
       </c>
       <c r="G21">
-        <v>-4.905378829664641</v>
+        <v>-8.240723665570508</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>-2.436885959260434</v>
       </c>
       <c r="E22">
-        <v>-22.68584093705902</v>
+        <v>-27.65554228119273</v>
       </c>
       <c r="F22">
-        <v>-2.63710696641741</v>
+        <v>-3.663752244630609</v>
       </c>
       <c r="G22">
-        <v>-5.272435566331334</v>
+        <v>-8.219526242482555</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>-1.595981346996531</v>
       </c>
       <c r="E23">
-        <v>-23.74323056090203</v>
+        <v>-28.23649115468874</v>
       </c>
       <c r="F23">
-        <v>-3.149180061556728</v>
+        <v>-3.180193774498778</v>
       </c>
       <c r="G23">
-        <v>-4.828299397873789</v>
+        <v>-7.632708871827962</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>-1.068765556559123</v>
       </c>
       <c r="E24">
-        <v>-24.4639553131188</v>
+        <v>-27.31976499047198</v>
       </c>
       <c r="F24">
-        <v>-2.587130750696845</v>
+        <v>-3.640838395593073</v>
       </c>
       <c r="G24">
-        <v>-4.27385254150219</v>
+        <v>-7.022452838755329</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>-0.878051161741132</v>
       </c>
       <c r="E25">
-        <v>-24.7504718635841</v>
+        <v>-28.48063477386427</v>
       </c>
       <c r="F25">
-        <v>-2.779570815746681</v>
+        <v>-3.190863993104052</v>
       </c>
       <c r="G25">
-        <v>-3.72903937264987</v>
+        <v>-7.467426575234309</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>-1.009405798960656</v>
       </c>
       <c r="E26">
-        <v>-25.24577370817305</v>
+        <v>-28.06675942040725</v>
       </c>
       <c r="F26">
-        <v>-2.531982943309413</v>
+        <v>-2.583515150091896</v>
       </c>
       <c r="G26">
-        <v>-5.381266440389334</v>
+        <v>-7.854972278243551</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>-1.4217860122654</v>
       </c>
       <c r="E27">
-        <v>-25.51634550165734</v>
+        <v>-28.83992843010685</v>
       </c>
       <c r="F27">
-        <v>-2.636253348928988</v>
+        <v>-2.621528051327232</v>
       </c>
       <c r="G27">
-        <v>-4.738861699584839</v>
+        <v>-7.751580630506572</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>-2.052983370662341</v>
       </c>
       <c r="E28">
-        <v>-25.67458396890737</v>
+        <v>-29.81137440999529</v>
       </c>
       <c r="F28">
-        <v>-2.421821151684402</v>
+        <v>-3.100563457364567</v>
       </c>
       <c r="G28">
-        <v>-5.001672667765422</v>
+        <v>-7.768040662927828</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>-2.820751087610587</v>
       </c>
       <c r="E29">
-        <v>-25.31985501446453</v>
+        <v>-30.42955413254537</v>
       </c>
       <c r="F29">
-        <v>-2.055778411595925</v>
+        <v>-2.670310944640513</v>
       </c>
       <c r="G29">
-        <v>-5.469211082640073</v>
+        <v>-9.788056097898165</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>-3.638637697452937</v>
       </c>
       <c r="E30">
-        <v>-24.26756445235415</v>
+        <v>-29.41543860631965</v>
       </c>
       <c r="F30">
-        <v>-2.45678066791477</v>
+        <v>-2.993377449154668</v>
       </c>
       <c r="G30">
-        <v>-5.66391419744123</v>
+        <v>-8.200914355460771</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>-4.421354715739855</v>
       </c>
       <c r="E31">
-        <v>-25.27644053415299</v>
+        <v>-29.07626043161915</v>
       </c>
       <c r="F31">
-        <v>-2.497378969057061</v>
+        <v>-3.004278888823595</v>
       </c>
       <c r="G31">
-        <v>-5.840333169228991</v>
+        <v>-9.262427540445922</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>-5.095784255394246</v>
       </c>
       <c r="E32">
-        <v>-24.4129465818964</v>
+        <v>-29.98001931051494</v>
       </c>
       <c r="F32">
-        <v>-2.069850430507562</v>
+        <v>-2.832010486018712</v>
       </c>
       <c r="G32">
-        <v>-6.020522852385983</v>
+        <v>-9.932981849970838</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>-5.607889055349812</v>
       </c>
       <c r="E33">
-        <v>-24.30424509181628</v>
+        <v>-27.39290437416987</v>
       </c>
       <c r="F33">
-        <v>-2.593978695075205</v>
+        <v>-3.083481605360638</v>
       </c>
       <c r="G33">
-        <v>-6.888071174225233</v>
+        <v>-9.040299866397442</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>-5.921980875962805</v>
       </c>
       <c r="E34">
-        <v>-23.39927937459744</v>
+        <v>-29.73141288020485</v>
       </c>
       <c r="F34">
-        <v>-2.786747379102495</v>
+        <v>-3.564541779410862</v>
       </c>
       <c r="G34">
-        <v>-5.879463817503177</v>
+        <v>-10.50860626615716</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>-6.02746366935926</v>
       </c>
       <c r="E35">
-        <v>-23.394293524715</v>
+        <v>-27.52565206123072</v>
       </c>
       <c r="F35">
-        <v>-2.353576888229243</v>
+        <v>-2.992606184373849</v>
       </c>
       <c r="G35">
-        <v>-6.13450493530309</v>
+        <v>-9.053095124906726</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>-5.934478217682221</v>
       </c>
       <c r="E36">
-        <v>-22.58447104639732</v>
+        <v>-26.88960524448338</v>
       </c>
       <c r="F36">
-        <v>-2.525773232414974</v>
+        <v>-2.601599487940299</v>
       </c>
       <c r="G36">
-        <v>-6.739606448971077</v>
+        <v>-9.915280362972355</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>-5.672900209719432</v>
       </c>
       <c r="E37">
-        <v>-21.96334555150525</v>
+        <v>-28.40311635580098</v>
       </c>
       <c r="F37">
-        <v>-2.50418890449345</v>
+        <v>-3.242633755773852</v>
       </c>
       <c r="G37">
-        <v>-5.898446485625358</v>
+        <v>-7.959045898361619</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>-5.287943029852915</v>
       </c>
       <c r="E38">
-        <v>-21.35396691818908</v>
+        <v>-27.05154800347168</v>
       </c>
       <c r="F38">
-        <v>-2.730753872756218</v>
+        <v>-3.57427286040828</v>
       </c>
       <c r="G38">
-        <v>-6.602427373460297</v>
+        <v>-8.429116880573813</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>-4.831488955059119</v>
       </c>
       <c r="E39">
-        <v>-21.52748445674099</v>
+        <v>-27.20217863438882</v>
       </c>
       <c r="F39">
-        <v>-2.728892226452619</v>
+        <v>-3.375249329867962</v>
       </c>
       <c r="G39">
-        <v>-6.939818311549581</v>
+        <v>-9.3769889688324</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>-4.357663702428448</v>
       </c>
       <c r="E40">
-        <v>-21.90212963986956</v>
+        <v>-25.78693993751168</v>
       </c>
       <c r="F40">
-        <v>-2.611973553539386</v>
+        <v>-3.183916275253019</v>
       </c>
       <c r="G40">
-        <v>-6.699466084307415</v>
+        <v>-8.911519644919792</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>-3.91742243041024</v>
       </c>
       <c r="E41">
-        <v>-21.06644504649407</v>
+        <v>-24.43939287010119</v>
       </c>
       <c r="F41">
-        <v>-2.880692814006363</v>
+        <v>-3.41400102991285</v>
       </c>
       <c r="G41">
-        <v>-6.943509569825868</v>
+        <v>-8.463996788375574</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>-3.551727679821539</v>
       </c>
       <c r="E42">
-        <v>-20.86858243167693</v>
+        <v>-24.86861975044422</v>
       </c>
       <c r="F42">
-        <v>-3.179483482395704</v>
+        <v>-3.32810953144195</v>
       </c>
       <c r="G42">
-        <v>-5.74872044252074</v>
+        <v>-8.607578458959305</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>-3.290373880027069</v>
       </c>
       <c r="E43">
-        <v>-19.26005940720441</v>
+        <v>-25.78238882113397</v>
       </c>
       <c r="F43">
-        <v>-2.853663705147558</v>
+        <v>-3.251971285851283</v>
       </c>
       <c r="G43">
-        <v>-6.356894142449171</v>
+        <v>-8.660782236320932</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>-3.151811701942586</v>
       </c>
       <c r="E44">
-        <v>-18.33091616725862</v>
+        <v>-24.93728047334852</v>
       </c>
       <c r="F44">
-        <v>-3.01617093654263</v>
+        <v>-3.512001543813201</v>
       </c>
       <c r="G44">
-        <v>-5.592866579622931</v>
+        <v>-8.961896216390883</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>-3.137840184699876</v>
       </c>
       <c r="E45">
-        <v>-18.926247474203</v>
+        <v>-23.81757904715996</v>
       </c>
       <c r="F45">
-        <v>-2.790942616072494</v>
+        <v>-3.862466160664458</v>
       </c>
       <c r="G45">
-        <v>-5.272501777242119</v>
+        <v>-9.33311430880044</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>-3.241287628298537</v>
       </c>
       <c r="E46">
-        <v>-17.54000912487097</v>
+        <v>-24.10717948842449</v>
       </c>
       <c r="F46">
-        <v>-2.859859954541714</v>
+        <v>-3.859038229210489</v>
       </c>
       <c r="G46">
-        <v>-6.305716418957577</v>
+        <v>-8.797772610735974</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>-3.447269780818529</v>
       </c>
       <c r="E47">
-        <v>-17.62328776187203</v>
+        <v>-23.12345002279024</v>
       </c>
       <c r="F47">
-        <v>-2.928662474332066</v>
+        <v>-3.921201853803319</v>
       </c>
       <c r="G47">
-        <v>-6.282711438005182</v>
+        <v>-8.446973963212642</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>-3.735774251135894</v>
       </c>
       <c r="E48">
-        <v>-17.03859836884568</v>
+        <v>-22.77173703203651</v>
       </c>
       <c r="F48">
-        <v>-2.9610848936859</v>
+        <v>-3.875519856672468</v>
       </c>
       <c r="G48">
-        <v>-6.57575430805039</v>
+        <v>-8.694685533188609</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>-4.088466164443908</v>
       </c>
       <c r="E49">
-        <v>-16.12950268333185</v>
+        <v>-23.2840115972062</v>
       </c>
       <c r="F49">
-        <v>-2.86913334452957</v>
+        <v>-3.825469206773877</v>
       </c>
       <c r="G49">
-        <v>-5.49257360251071</v>
+        <v>-8.162558374842776</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>-4.484641217769332</v>
       </c>
       <c r="E50">
-        <v>-17.13091131149204</v>
+        <v>-21.77955743390395</v>
       </c>
       <c r="F50">
-        <v>-3.179459726806972</v>
+        <v>-3.51854779221467</v>
       </c>
       <c r="G50">
-        <v>-6.118313057070514</v>
+        <v>-9.293682400882179</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>-4.907987013270027</v>
       </c>
       <c r="E51">
-        <v>-16.10090989844742</v>
+        <v>-20.74763594788007</v>
       </c>
       <c r="F51">
-        <v>-2.969499123214629</v>
+        <v>-3.960825383954656</v>
       </c>
       <c r="G51">
-        <v>-5.934551295276649</v>
+        <v>-8.742817554784072</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>-5.346649615978275</v>
       </c>
       <c r="E52">
-        <v>-14.65810638028559</v>
+        <v>-21.85352552834524</v>
       </c>
       <c r="F52">
-        <v>-3.347482214052563</v>
+        <v>-4.210783272294379</v>
       </c>
       <c r="G52">
-        <v>-5.550091020710008</v>
+        <v>-8.589165204669879</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>-5.787057634946057</v>
       </c>
       <c r="E53">
-        <v>-13.59999672907536</v>
+        <v>-20.13186310926507</v>
       </c>
       <c r="F53">
-        <v>-3.073488421034215</v>
+        <v>-3.903446926785327</v>
       </c>
       <c r="G53">
-        <v>-5.572493482374256</v>
+        <v>-7.432344724154651</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>-6.225427411779938</v>
       </c>
       <c r="E54">
-        <v>-13.68554413155426</v>
+        <v>-20.27350471927699</v>
       </c>
       <c r="F54">
-        <v>-3.301340942206234</v>
+        <v>-3.575033039247691</v>
       </c>
       <c r="G54">
-        <v>-7.006035843426083</v>
+        <v>-8.652863411390996</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>-6.656451022416655</v>
       </c>
       <c r="E55">
-        <v>-13.27189520179762</v>
+        <v>-20.65545885945394</v>
       </c>
       <c r="F55">
-        <v>-3.122746426122128</v>
+        <v>-4.3407841479221</v>
       </c>
       <c r="G55">
-        <v>-5.032818280198884</v>
+        <v>-7.633274975115177</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>-7.074435482073369</v>
       </c>
       <c r="E56">
-        <v>-11.39544501266127</v>
+        <v>-17.88198136803421</v>
       </c>
       <c r="F56">
-        <v>-3.226088780075256</v>
+        <v>-4.395277092913497</v>
       </c>
       <c r="G56">
-        <v>-5.087402555050388</v>
+        <v>-7.298813869828148</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>-7.479525924006945</v>
       </c>
       <c r="E57">
-        <v>-12.44411732403952</v>
+        <v>-18.98486404175828</v>
       </c>
       <c r="F57">
-        <v>-3.190612183863497</v>
+        <v>-4.058505989260087</v>
       </c>
       <c r="G57">
-        <v>-5.72959542094037</v>
+        <v>-8.189092397340035</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>-7.867768172930768</v>
       </c>
       <c r="E58">
-        <v>-12.05286622672482</v>
+        <v>-17.89454788340549</v>
       </c>
       <c r="F58">
-        <v>-3.506795110616194</v>
+        <v>-4.169432710842255</v>
       </c>
       <c r="G58">
-        <v>-6.267909988899101</v>
+        <v>-8.934143913135172</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>-8.238720161604753</v>
       </c>
       <c r="E59">
-        <v>-12.09772981871881</v>
+        <v>-18.11533363364946</v>
       </c>
       <c r="F59">
-        <v>-3.550753243858089</v>
+        <v>-4.326349460355827</v>
       </c>
       <c r="G59">
-        <v>-6.212958243492738</v>
+        <v>-8.567928055035454</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>-8.592130172495574</v>
       </c>
       <c r="E60">
-        <v>-11.41597258533804</v>
+        <v>-18.7877440966784</v>
       </c>
       <c r="F60">
-        <v>-3.539408366532838</v>
+        <v>-4.602181144089042</v>
       </c>
       <c r="G60">
-        <v>-6.724232275486702</v>
+        <v>-8.238863138977438</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>-8.921840491488032</v>
       </c>
       <c r="E61">
-        <v>-10.17896556845479</v>
+        <v>-17.3041073283894</v>
       </c>
       <c r="F61">
-        <v>-3.798650730801826</v>
+        <v>-4.401191442654707</v>
       </c>
       <c r="G61">
-        <v>-6.555010429701316</v>
+        <v>-8.147488771548014</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>-9.223102522011713</v>
       </c>
       <c r="E62">
-        <v>-10.31985998025544</v>
+        <v>-16.11519270546761</v>
       </c>
       <c r="F62">
-        <v>-3.677214536764802</v>
+        <v>-4.274397571505751</v>
       </c>
       <c r="G62">
-        <v>-6.625316485318818</v>
+        <v>-9.467995865706966</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>-9.488036380409254</v>
       </c>
       <c r="E63">
-        <v>-10.78603920850106</v>
+        <v>-16.724113962909</v>
       </c>
       <c r="F63">
-        <v>-3.538237216008371</v>
+        <v>-4.433035017496447</v>
       </c>
       <c r="G63">
-        <v>-6.661447779334424</v>
+        <v>-10.17852501261858</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>-9.703415252589952</v>
       </c>
       <c r="E64">
-        <v>-8.661329017316211</v>
+        <v>-15.91867051895674</v>
       </c>
       <c r="F64">
-        <v>-3.328437358566446</v>
+        <v>-4.288896399161599</v>
       </c>
       <c r="G64">
-        <v>-7.291371763455866</v>
+        <v>-10.26027231361981</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>-9.858368485658787</v>
       </c>
       <c r="E65">
-        <v>-9.590902462292728</v>
+        <v>-15.7325592941895</v>
       </c>
       <c r="F65">
-        <v>-3.643608297239177</v>
+        <v>-4.927856012245925</v>
       </c>
       <c r="G65">
-        <v>-7.401394433908005</v>
+        <v>-10.55302385565756</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>-9.941090211888326</v>
       </c>
       <c r="E66">
-        <v>-9.145599499222472</v>
+        <v>-15.22477244676141</v>
       </c>
       <c r="F66">
-        <v>-4.04401032901607</v>
+        <v>-4.709192152795286</v>
       </c>
       <c r="G66">
-        <v>-7.940629333526654</v>
+        <v>-9.644361868766099</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>-9.938815387597831</v>
       </c>
       <c r="E67">
-        <v>-9.499123879579274</v>
+        <v>-14.71175974032847</v>
       </c>
       <c r="F67">
-        <v>-4.081523571035085</v>
+        <v>-4.417208252430503</v>
       </c>
       <c r="G67">
-        <v>-8.720189976023153</v>
+        <v>-10.22647826475493</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>-9.841649066735236</v>
       </c>
       <c r="E68">
-        <v>-9.16035779601347</v>
+        <v>-15.29369582115816</v>
       </c>
       <c r="F68">
-        <v>-3.894351703712958</v>
+        <v>-4.424984248475311</v>
       </c>
       <c r="G68">
-        <v>-9.040925559504364</v>
+        <v>-10.77680349193013</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>-9.644560106234454</v>
       </c>
       <c r="E69">
-        <v>-10.19318044836487</v>
+        <v>-16.22261263740356</v>
       </c>
       <c r="F69">
-        <v>-3.664792739417052</v>
+        <v>-4.954547791744742</v>
       </c>
       <c r="G69">
-        <v>-8.223339990943796</v>
+        <v>-10.54267840084733</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>-9.345201961613689</v>
       </c>
       <c r="E70">
-        <v>-8.407521634608312</v>
+        <v>-14.31805873857562</v>
       </c>
       <c r="F70">
-        <v>-4.297306669425541</v>
+        <v>-4.955157518522186</v>
       </c>
       <c r="G70">
-        <v>-8.897900060571232</v>
+        <v>-10.75689387105696</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>-8.948570066481196</v>
       </c>
       <c r="E71">
-        <v>-10.14945350334681</v>
+        <v>-14.51356654690877</v>
       </c>
       <c r="F71">
-        <v>-4.495438573535465</v>
+        <v>-5.106418854211723</v>
       </c>
       <c r="G71">
-        <v>-8.714373347510655</v>
+        <v>-11.09752252268365</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>-8.466371661800233</v>
       </c>
       <c r="E72">
-        <v>-9.77402942268891</v>
+        <v>-17.77289948613745</v>
       </c>
       <c r="F72">
-        <v>-4.562959875240226</v>
+        <v>-5.075647448274735</v>
       </c>
       <c r="G72">
-        <v>-9.2654268947045</v>
+        <v>-10.85048961454323</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>-7.91159819098664</v>
       </c>
       <c r="E73">
-        <v>-9.68175723630862</v>
+        <v>-16.77258674868711</v>
       </c>
       <c r="F73">
-        <v>-4.753303113658021</v>
+        <v>-5.028263759137744</v>
       </c>
       <c r="G73">
-        <v>-8.259686470419453</v>
+        <v>-11.31346940821031</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>-7.308350524267375</v>
       </c>
       <c r="E74">
-        <v>-9.953633230307124</v>
+        <v>-16.19788264084767</v>
       </c>
       <c r="F74">
-        <v>-4.841349244026876</v>
+        <v>-5.088781121431474</v>
       </c>
       <c r="G74">
-        <v>-8.207919469821869</v>
+        <v>-10.49969758811098</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>-6.680096335720712</v>
       </c>
       <c r="E75">
-        <v>-9.183534525984726</v>
+        <v>-15.90791992166253</v>
       </c>
       <c r="F75">
-        <v>-4.143236631294972</v>
+        <v>-5.485591308192151</v>
       </c>
       <c r="G75">
-        <v>-8.472051345672622</v>
+        <v>-10.36438897082989</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>-6.048283355065004</v>
       </c>
       <c r="E76">
-        <v>-10.28980902674054</v>
+        <v>-17.25000564941977</v>
       </c>
       <c r="F76">
-        <v>-4.418905985171854</v>
+        <v>-5.387787965678273</v>
       </c>
       <c r="G76">
-        <v>-8.985871187186284</v>
+        <v>-10.56842451350625</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>-5.438542025547488</v>
       </c>
       <c r="E77">
-        <v>-10.48536664828778</v>
+        <v>-16.79301922340972</v>
       </c>
       <c r="F77">
-        <v>-4.959089068457264</v>
+        <v>-5.278833749813785</v>
       </c>
       <c r="G77">
-        <v>-8.585099854747654</v>
+        <v>-10.86841621863838</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>-4.867990074388821</v>
       </c>
       <c r="E78">
-        <v>-11.77878486588458</v>
+        <v>-17.65470178606324</v>
       </c>
       <c r="F78">
-        <v>-4.559246876721478</v>
+        <v>-5.655408926092892</v>
       </c>
       <c r="G78">
-        <v>-7.679149204652858</v>
+        <v>-9.97585672524994</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>-4.349476948264456</v>
       </c>
       <c r="E79">
-        <v>-12.44975074570506</v>
+        <v>-18.56509261514327</v>
       </c>
       <c r="F79">
-        <v>-5.129236889041374</v>
+        <v>-5.611999546950697</v>
       </c>
       <c r="G79">
-        <v>-8.516578183175818</v>
+        <v>-10.85189328585188</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>-3.893803648068281</v>
       </c>
       <c r="E80">
-        <v>-12.64933418064512</v>
+        <v>-19.04029256361217</v>
       </c>
       <c r="F80">
-        <v>-5.102411286392703</v>
+        <v>-5.763131810608126</v>
       </c>
       <c r="G80">
-        <v>-8.614047264943041</v>
+        <v>-9.603642158633063</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>-3.502058319946325</v>
       </c>
       <c r="E81">
-        <v>-13.25720030364273</v>
+        <v>-19.3712877857808</v>
       </c>
       <c r="F81">
-        <v>-4.999787934925185</v>
+        <v>-5.69992135640519</v>
       </c>
       <c r="G81">
-        <v>-7.874180063462402</v>
+        <v>-10.18101785340965</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>-3.176826830039147</v>
       </c>
       <c r="E82">
-        <v>-13.9325859740947</v>
+        <v>-18.84934492860474</v>
       </c>
       <c r="F82">
-        <v>-5.273902881446064</v>
+        <v>-5.917507503980374</v>
       </c>
       <c r="G82">
-        <v>-6.669992297371283</v>
+        <v>-9.583586873756158</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>-2.917501487840858</v>
       </c>
       <c r="E83">
-        <v>-15.54812360480511</v>
+        <v>-20.9032795995237</v>
       </c>
       <c r="F83">
-        <v>-5.170559735639978</v>
+        <v>-5.876770628570483</v>
       </c>
       <c r="G83">
-        <v>-8.169325129925046</v>
+        <v>-10.75710243542593</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>-2.720544379750675</v>
       </c>
       <c r="E84">
-        <v>-16.24820757249491</v>
+        <v>-20.15721350676001</v>
       </c>
       <c r="F84">
-        <v>-5.265513199359024</v>
+        <v>-5.761746859785074</v>
       </c>
       <c r="G84">
-        <v>-7.139205848288806</v>
+        <v>-10.01765236268324</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>-2.588491140072028</v>
       </c>
       <c r="E85">
-        <v>-16.54141720754355</v>
+        <v>-21.92142093914224</v>
       </c>
       <c r="F85">
-        <v>-5.330684281485272</v>
+        <v>-5.364654773371448</v>
       </c>
       <c r="G85">
-        <v>-8.234559429776384</v>
+        <v>-9.871544745853045</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>-2.51945642695119</v>
       </c>
       <c r="E86">
-        <v>-17.19024337794054</v>
+        <v>-22.20391167621472</v>
       </c>
       <c r="F86">
-        <v>-5.3518227961916</v>
+        <v>-5.939559025146953</v>
       </c>
       <c r="G86">
-        <v>-8.097108889531384</v>
+        <v>-9.606545507071004</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>-2.515756305120971</v>
       </c>
       <c r="E87">
-        <v>-19.43272559264287</v>
+        <v>-24.74079451462971</v>
       </c>
       <c r="F87">
-        <v>-5.824722925512523</v>
+        <v>-6.30137564600008</v>
       </c>
       <c r="G87">
-        <v>-7.502392557220091</v>
+        <v>-10.0885278321335</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>-2.581413441879648</v>
       </c>
       <c r="E88">
-        <v>-21.52022078443268</v>
+        <v>-25.85056952579345</v>
       </c>
       <c r="F88">
-        <v>-5.526903068849347</v>
+        <v>-5.74078413643536</v>
       </c>
       <c r="G88">
-        <v>-7.982530908417209</v>
+        <v>-10.31291991933084</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>-2.720888697766531</v>
       </c>
       <c r="E89">
-        <v>-21.51158498450005</v>
+        <v>-25.41377556538361</v>
       </c>
       <c r="F89">
-        <v>-5.863658335443602</v>
+        <v>-6.315689180063822</v>
       </c>
       <c r="G89">
-        <v>-7.369100062172415</v>
+        <v>-10.50498452933719</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>-2.941630490903319</v>
       </c>
       <c r="E90">
-        <v>-23.60855827238792</v>
+        <v>-26.12784798928311</v>
       </c>
       <c r="F90">
-        <v>-5.719944942147049</v>
+        <v>-6.081397310639626</v>
       </c>
       <c r="G90">
-        <v>-7.983315507710016</v>
+        <v>-9.951458004625511</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>-3.245664148042604</v>
       </c>
       <c r="E91">
-        <v>-25.50822141928758</v>
+        <v>-29.62009166791129</v>
       </c>
       <c r="F91">
-        <v>-5.459617739325986</v>
+        <v>-5.973022731140189</v>
       </c>
       <c r="G91">
-        <v>-8.368699424482115</v>
+        <v>-9.85621360946068</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>-3.637217843084851</v>
       </c>
       <c r="E92">
-        <v>-27.07662669252616</v>
+        <v>-32.58381035239326</v>
       </c>
       <c r="F92">
-        <v>-5.429634227081929</v>
+        <v>-6.682351941018194</v>
       </c>
       <c r="G92">
-        <v>-8.314022454355511</v>
+        <v>-10.39664030547346</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>-4.11721256367376</v>
       </c>
       <c r="E93">
-        <v>-28.74696338720338</v>
+        <v>-33.5675964239526</v>
       </c>
       <c r="F93">
-        <v>-5.436292126750437</v>
+        <v>-6.184095096285169</v>
       </c>
       <c r="G93">
-        <v>-8.005986123562945</v>
+        <v>-10.90443495410566</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>-4.676917164746379</v>
       </c>
       <c r="E94">
-        <v>-30.67087198394011</v>
+        <v>-35.47328696975647</v>
       </c>
       <c r="F94">
-        <v>-5.36162276839634</v>
+        <v>-5.650415501341511</v>
       </c>
       <c r="G94">
-        <v>-9.245775496383386</v>
+        <v>-9.315141357067736</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>-5.310771103697884</v>
       </c>
       <c r="E95">
-        <v>-32.76428136278394</v>
+        <v>-36.75741955140055</v>
       </c>
       <c r="F95">
-        <v>-5.338924303363304</v>
+        <v>-5.860959700563694</v>
       </c>
       <c r="G95">
-        <v>-8.521583728031198</v>
+        <v>-10.46048748674385</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>-6.009651033612398</v>
       </c>
       <c r="E96">
-        <v>-35.73890008420237</v>
+        <v>-41.05019780815668</v>
       </c>
       <c r="F96">
-        <v>-4.829605272810936</v>
+        <v>-5.421569996560511</v>
       </c>
       <c r="G96">
-        <v>-8.891341869857936</v>
+        <v>-10.76545825236705</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>-6.747474918119131</v>
       </c>
       <c r="E97">
-        <v>-37.83506277524286</v>
+        <v>-41.57421697066527</v>
       </c>
       <c r="F97">
-        <v>-5.079640762740516</v>
+        <v>-5.3803540501112</v>
       </c>
       <c r="G97">
-        <v>-8.93537543607578</v>
+        <v>-11.73684845613662</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>-7.520190605989236</v>
       </c>
       <c r="E98">
-        <v>-40.47822663438087</v>
+        <v>-41.57168555369498</v>
       </c>
       <c r="F98">
-        <v>-4.547229716235124</v>
+        <v>-5.611226698463962</v>
       </c>
       <c r="G98">
-        <v>-9.244921375634254</v>
+        <v>-11.01221969577325</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>-8.279807434766598</v>
       </c>
       <c r="E99">
-        <v>-41.57586080673005</v>
+        <v>-44.7855254430426</v>
       </c>
       <c r="F99">
-        <v>-4.320742349562213</v>
+        <v>-4.541191837432511</v>
       </c>
       <c r="G99">
-        <v>-9.666400170421026</v>
+        <v>-11.85676634720564</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>-9.035949709834114</v>
       </c>
       <c r="E100">
-        <v>-44.45069686762646</v>
+        <v>-46.82884084241358</v>
       </c>
       <c r="F100">
-        <v>-4.605635206690615</v>
+        <v>-4.675753786096697</v>
       </c>
       <c r="G100">
-        <v>-10.25026784500013</v>
+        <v>-10.80403603953618</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>-9.71036497633647</v>
       </c>
       <c r="E101">
-        <v>-46.210364504816</v>
+        <v>-49.61921180611893</v>
       </c>
       <c r="F101">
-        <v>-4.303485498054627</v>
+        <v>-4.70999271613554</v>
       </c>
       <c r="G101">
-        <v>-9.15723164539004</v>
+        <v>-11.14571082355328</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>-10.36624453454606</v>
       </c>
       <c r="E102">
-        <v>-49.09126985300119</v>
+        <v>-51.6861964070095</v>
       </c>
       <c r="F102">
-        <v>-3.400032743738674</v>
+        <v>-4.058425220258401</v>
       </c>
       <c r="G102">
-        <v>-11.28304880524994</v>
+        <v>-11.56059501162582</v>
       </c>
     </row>
   </sheetData>
